--- a/ConfigDirectory/mydb_misc_tbl.xlsx
+++ b/ConfigDirectory/mydb_misc_tbl.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\服务端扩展配置\策划配置\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\excel2flatbuffers\ConfigDirectory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16E1D8F-F729-4C27-AB59-91A58EB24A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F877751-CE42-4859-AFCB-95AFADDB3E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ConfigDirectory/mydb_misc_tbl.xlsx
+++ b/ConfigDirectory/mydb_misc_tbl.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\excel2flatbuffers\ConfigDirectory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F877751-CE42-4859-AFCB-95AFADDB3E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15F8A4C-29BD-4C15-B760-7D0149BC0A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_172.16.1.230_10097_mydb_Moon_Gamecfg_chenmo_Config_Chat" localSheetId="0" hidden="1">misc_infos!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">misc_infos!$A$1:$D$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">misc_infos!$A$1:$F$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">type1_datas!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">type2_datas!$A$1:$B$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">type3_datas!$A$1:$C$25</definedName>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="37">
   <si>
     <t>打磨等级对应概率</t>
   </si>
@@ -174,10 +174,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>大家好</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -195,6 +191,34 @@
   </si>
   <si>
     <t>字段4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整数列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23,34,54,6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字符串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渣渣灰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>helloworld</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -586,21 +610,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="3" width="20.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="71.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="38.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.875" style="1" customWidth="1"/>
-    <col min="8" max="11" width="16.125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.375" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="13.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.875" style="1" customWidth="1"/>
+    <col min="7" max="10" width="16.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.375" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -611,10 +634,16 @@
         <v>5</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>30</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -627,8 +656,14 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -638,8 +673,14 @@
       <c r="D3" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -649,8 +690,14 @@
       <c r="D4" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -660,8 +707,14 @@
       <c r="D5" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -674,8 +727,14 @@
       <c r="D6" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -685,8 +744,14 @@
       <c r="D7" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -696,8 +761,14 @@
       <c r="D8" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -707,8 +778,14 @@
       <c r="D9" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>10</v>
       </c>
@@ -721,8 +798,14 @@
       <c r="D10" s="1">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>11</v>
       </c>
@@ -735,8 +818,14 @@
       <c r="D11" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>12</v>
       </c>
@@ -749,8 +838,14 @@
       <c r="D12" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>13</v>
       </c>
@@ -763,8 +858,14 @@
       <c r="D13" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>14</v>
       </c>
@@ -777,8 +878,14 @@
       <c r="D14" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>15</v>
       </c>
@@ -791,8 +898,14 @@
       <c r="D15" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>16</v>
       </c>
@@ -805,8 +918,14 @@
       <c r="D16" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>17</v>
       </c>
@@ -819,8 +938,14 @@
       <c r="D17" s="1">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>18</v>
       </c>
@@ -833,8 +958,14 @@
       <c r="D18" s="1">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>19</v>
       </c>
@@ -847,8 +978,14 @@
       <c r="D19" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>20</v>
       </c>
@@ -861,8 +998,14 @@
       <c r="D20" s="1">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>21</v>
       </c>
@@ -875,8 +1018,14 @@
       <c r="D21" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>22</v>
       </c>
@@ -889,8 +1038,14 @@
       <c r="D22" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E22" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>23</v>
       </c>
@@ -903,8 +1058,14 @@
       <c r="D23" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>24</v>
       </c>
@@ -917,8 +1078,14 @@
       <c r="D24" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>25</v>
       </c>
@@ -931,8 +1098,14 @@
       <c r="D25" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E25" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>26</v>
       </c>
@@ -945,8 +1118,14 @@
       <c r="D26" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>27</v>
       </c>
@@ -959,8 +1138,14 @@
       <c r="D27" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>28</v>
       </c>
@@ -973,8 +1158,14 @@
       <c r="D28" s="1">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="E28" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>29</v>
       </c>
@@ -987,9 +1178,15 @@
       <c r="D29" s="1">
         <v>28</v>
       </c>
+      <c r="E29" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D29" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F29" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
@@ -1015,7 +1212,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
@@ -1023,7 +1220,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.15">
@@ -1031,7 +1228,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.15">
@@ -1039,7 +1236,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.15">
@@ -1047,7 +1244,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.15">
@@ -1055,7 +1252,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.15">
@@ -1063,7 +1260,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1297,10 +1494,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
@@ -1585,16 +1782,16 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">

--- a/ConfigDirectory/mydb_misc_tbl.xlsx
+++ b/ConfigDirectory/mydb_misc_tbl.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\excel2flatbuffers\ConfigDirectory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15F8A4C-29BD-4C15-B760-7D0149BC0A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1931017E-C410-4C0A-B22F-84E68C9E8190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9450" yWindow="3645" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc_infos" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="37">
   <si>
     <t>打磨等级对应概率</t>
   </si>
@@ -693,9 +693,7 @@
       <c r="E4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
@@ -710,9 +708,7 @@
       <c r="E5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
